--- a/PO_TBD_20260622.xlsx
+++ b/PO_TBD_20260622.xlsx
@@ -3190,7 +3190,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 08:03</t>
+          <t>Generated: 2026-06-22 10:55</t>
         </is>
       </c>
     </row>
